--- a/sample_data/projects/itg_015/engagement_workbook.xlsx
+++ b/sample_data/projects/itg_015/engagement_workbook.xlsx
@@ -512,17 +512,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Power User</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>23/11/2024</t>
+          <t>11/06/2024</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -550,17 +550,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Read Only</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>03/10/2024</t>
+          <t>28/06/2024</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -588,17 +588,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Concur</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Read Only</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>04/07/2024</t>
+          <t>28/04/2024</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -631,12 +631,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10/12/2024</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -664,12 +664,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>12/05/2024</t>
+          <t>17/03/2024</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -702,30 +702,34 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Concur</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Read Only</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>19/07/2024</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>15/09/2024</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>28/06/2024</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -745,7 +749,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Concur</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20/02/2024</t>
+          <t>16/02/2024</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -778,17 +782,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Concur</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -798,7 +802,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>05/10/2024</t>
+          <t>13/12/2024</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -821,12 +825,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Power User</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -836,7 +840,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>01/11/2024</t>
+          <t>21/06/2024</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -859,12 +863,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Read Only</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -874,7 +878,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>03/03/2024</t>
+          <t>03/10/2024</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -897,12 +901,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>Concur</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Power User</t>
+          <t>Read Only</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -912,7 +916,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>14/11/2024</t>
+          <t>04/07/2024</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -930,12 +934,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -950,7 +954,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>28/07/2024</t>
+          <t>10/12/2024</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -968,17 +972,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Read Only</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -988,7 +992,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>19/06/2024</t>
+          <t>12/05/2024</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1006,17 +1010,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SAP ERP</t>
+          <t>Concur</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1026,7 +1030,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>01/05/2024</t>
+          <t>19/07/2024</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1044,17 +1048,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>Concur</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1064,7 +1068,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>25/05/2024</t>
+          <t>20/02/2024</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1087,12 +1091,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>Concur</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1102,7 +1106,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>07/11/2024</t>
+          <t>05/10/2024</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1120,17 +1124,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SAP ERP</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Read Only</t>
+          <t>Power User</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1140,7 +1144,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>26/05/2024</t>
+          <t>01/11/2024</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1158,7 +1162,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1168,7 +1172,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1178,7 +1182,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10/02/2024</t>
+          <t>03/03/2024</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -1196,17 +1200,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Concur</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Power User</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1216,7 +1220,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>26/03/2024</t>
+          <t>14/11/2024</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1234,17 +1238,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1254,7 +1258,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>27/05/2024</t>
+          <t>28/07/2024</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -1272,17 +1276,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Power User</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1292,7 +1296,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>15/02/2024</t>
+          <t>19/06/2024</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -1310,34 +1314,30 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>SAP ERP</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Terminated</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>03/06/2024</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>25/03/2024</t>
-        </is>
-      </c>
+          <t>01/05/2024</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1357,12 +1357,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>15/02/2024</t>
+          <t>25/05/2024</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>12/11/2024</t>
+          <t>07/11/2024</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>SAP ERP</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>18/10/2024</t>
+          <t>26/05/2024</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Concur</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Read Only</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>27/11/2024</t>
+          <t>10/02/2024</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -1504,17 +1504,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>Concur</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Read Only</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>02/03/2024</t>
+          <t>26/03/2024</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -1542,34 +1542,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SAP ERP</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Terminated</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>05/09/2024</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>16/05/2024</t>
-        </is>
-      </c>
+          <t>27/05/2024</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1584,17 +1580,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Power User</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1604,7 +1600,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>24/10/2024</t>
+          <t>15/02/2024</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -1622,30 +1618,34 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SAP ERP</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>14/10/2024</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>03/06/2024</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>25/03/2024</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1660,17 +1660,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SAP ERP</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Power User</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>15/04/2024</t>
+          <t>15/02/2024</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -1698,17 +1698,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Read Only</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1736,17 +1736,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SAP ERP</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Read Only</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>07/05/2024</t>
+          <t>18/10/2024</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -1774,12 +1774,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>Concur</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1789,19 +1789,15 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Terminated</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>26/01/2024</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>03/08/2024</t>
-        </is>
-      </c>
+          <t>27/11/2024</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1816,17 +1812,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Read Only</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1836,7 +1832,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>27/02/2024</t>
+          <t>02/03/2024</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -1854,12 +1850,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>SAP ERP</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1869,15 +1865,19 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>11/04/2024</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>05/09/2024</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>16/05/2024</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1892,17 +1892,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SAP ERP</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Power User</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>05/03/2024</t>
+          <t>24/10/2024</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Read Only</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>01/03/2024</t>
+          <t>14/10/2024</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>SAP ERP</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>06/01/2024</t>
+          <t>15/04/2024</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -2011,12 +2011,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Read Only</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>24/02/2024</t>
+          <t>12/11/2024</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -2044,17 +2044,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>SAP ERP</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>04/10/2024</t>
+          <t>07/05/2024</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -2097,15 +2097,19 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>26/01/2024</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>03/08/2024</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2120,17 +2124,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2140,7 +2144,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>01/11/2024</t>
+          <t>27/02/2024</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -2158,17 +2162,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2178,7 +2182,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>04/11/2024</t>
+          <t>11/04/2024</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -2196,7 +2200,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2206,7 +2210,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Read Only</t>
+          <t>Power User</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2216,7 +2220,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20/06/2024</t>
+          <t>05/03/2024</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -2239,12 +2243,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>SAP ERP</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Read Only</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2254,7 +2258,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>19/11/2024</t>
+          <t>01/03/2024</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -2272,17 +2276,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Power User</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2292,7 +2296,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>10/09/2024</t>
+          <t>06/01/2024</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -2310,7 +2314,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2320,7 +2324,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Read Only</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2330,7 +2334,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>04/12/2024</t>
+          <t>24/02/2024</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -2348,17 +2352,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Concur</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2368,7 +2372,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>08/08/2024</t>
+          <t>04/10/2024</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -2386,17 +2390,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Read Only</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2406,7 +2410,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>04/12/2024</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -2424,7 +2428,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2434,7 +2438,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Power User</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2444,7 +2448,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>22/03/2024</t>
+          <t>01/11/2024</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -2462,17 +2466,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>SAP ERP</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Read Only</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2482,7 +2486,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>14/02/2024</t>
+          <t>04/11/2024</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -2500,17 +2504,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Concur</t>
+          <t>SAP ERP</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Read Only</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2520,7 +2524,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>19/01/2024</t>
+          <t>20/06/2024</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -2538,34 +2542,30 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Power User</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Terminated</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>25/11/2024</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>11/09/2024</t>
-        </is>
-      </c>
+          <t>19/11/2024</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2580,12 +2580,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>12/05/2024</t>
+          <t>10/09/2024</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -2623,12 +2623,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Concur</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Read Only</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>16/11/2024</t>
+          <t>04/12/2024</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
@@ -2656,17 +2656,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>Concur</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>04/06/2024</t>
+          <t>08/08/2024</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
@@ -2694,12 +2694,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Concur</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>25/09/2024</t>
+          <t>04/12/2024</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -2732,17 +2732,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Read Only</t>
+          <t>Power User</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>22/10/2024</t>
+          <t>22/03/2024</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Read Only</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>23/05/2024</t>
+          <t>14/02/2024</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -2813,12 +2813,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>Concur</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Read Only</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>28/03/2024</t>
+          <t>19/01/2024</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -2846,30 +2846,34 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SAP ERP</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Power User</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>21/12/2024</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>25/11/2024</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>11/09/2024</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2884,34 +2888,30 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Concur</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Terminated</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>15/07/2024</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>24/02/2024</t>
-        </is>
-      </c>
+          <t>12/05/2024</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2926,17 +2926,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>Concur</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Power User</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20/10/2024</t>
+          <t>16/11/2024</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
@@ -2969,12 +2969,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Concur</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>02/10/2024</t>
+          <t>04/06/2024</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>Concur</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20/08/2024</t>
+          <t>25/09/2024</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
@@ -3040,17 +3040,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Concur</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Read Only</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>12/02/2024</t>
+          <t>22/10/2024</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -3083,12 +3083,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>SAP ERP</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>22/09/2024</t>
+          <t>23/05/2024</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -3116,17 +3116,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Read Only</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>28/03/2024</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -3154,17 +3154,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Concur</t>
+          <t>SAP ERP</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Power User</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>11/05/2024</t>
+          <t>21/12/2024</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -3192,30 +3192,34 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>Concur</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>13/03/2024</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>15/07/2024</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>24/02/2024</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3230,17 +3234,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Power User</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3250,7 +3254,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>26/11/2024</t>
+          <t>20/10/2024</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -3268,17 +3272,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SAP ERP</t>
+          <t>Concur</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3288,7 +3292,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>15/01/2024</t>
+          <t>02/10/2024</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -3311,7 +3315,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3326,7 +3330,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>13/10/2024</t>
+          <t>20/08/2024</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -3344,17 +3348,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>Concur</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Read Only</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3364,7 +3368,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>01/07/2024</t>
+          <t>12/02/2024</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -3382,34 +3386,30 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Power User</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Terminated</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>14/02/2024</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>26/03/2024</t>
-        </is>
-      </c>
+          <t>22/09/2024</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>17/07/2024</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
@@ -3462,17 +3462,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>Concur</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Power User</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>25/06/2024</t>
+          <t>11/05/2024</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -3500,17 +3500,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SAP ERP</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>07/09/2024</t>
+          <t>13/03/2024</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -3538,17 +3538,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>04/04/2024</t>
+          <t>26/11/2024</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -3576,17 +3576,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Concur</t>
+          <t>SAP ERP</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>25/03/2024</t>
+          <t>15/01/2024</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -3614,12 +3614,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Concur</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>25/08/2024</t>
+          <t>13/10/2024</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -3652,17 +3652,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Read Only</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>21/11/2024</t>
+          <t>01/07/2024</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -3690,17 +3690,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Concur</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Power User</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>16/02/2024</t>
+          <t>14/02/2024</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>28/06/2024</t>
+          <t>26/03/2024</t>
         </is>
       </c>
     </row>
@@ -3732,12 +3732,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>12/01/2024</t>
+          <t>17/07/2024</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
@@ -3775,12 +3775,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>02/01/2024</t>
+          <t>25/06/2024</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Read Only</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20/10/2024</t>
+          <t>07/09/2024</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
@@ -3846,17 +3846,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>02/12/2024</t>
+          <t>04/04/2024</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Power User</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>16/10/2024</t>
+          <t>25/03/2024</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>Concur</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Read Only</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>23/06/2024</t>
+          <t>25/08/2024</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
@@ -3960,17 +3960,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SAP ERP</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>15/12/2024</t>
+          <t>21/11/2024</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Power User</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4018,12 +4018,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>10/06/2024</t>
+          <t>16/02/2024</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>17/09/2024</t>
+          <t>28/06/2024</t>
         </is>
       </c>
     </row>
@@ -4045,12 +4045,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Read Only</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>21/11/2024</t>
+          <t>12/01/2024</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -4083,12 +4083,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>SAP ERP</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>13/11/2024</t>
+          <t>02/01/2024</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -4116,17 +4116,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Concur</t>
+          <t>SAP ERP</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Power User</t>
+          <t>Read Only</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>20/10/2024</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -4154,17 +4154,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20/03/2024</t>
+          <t>02/12/2024</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
@@ -4192,17 +4192,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>Concur</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Power User</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>21/07/2024</t>
+          <t>16/10/2024</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
@@ -4230,12 +4230,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>22/11/2024</t>
+          <t>23/06/2024</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Power User</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>06/05/2024</t>
+          <t>15/12/2024</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Power User</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>05/03/2024</t>
+          <t>10/06/2024</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>25/06/2024</t>
+          <t>17/09/2024</t>
         </is>
       </c>
     </row>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Read Only</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>21/11/2024</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
@@ -4391,12 +4391,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>SAP ERP</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>13/10/2024</t>
+          <t>13/11/2024</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
@@ -4424,17 +4424,17 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>Concur</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Power User</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>15/12/2024</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Concur</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>10/10/2024</t>
+          <t>20/03/2024</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
@@ -4500,12 +4500,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Concur</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>10/04/2024</t>
+          <t>21/07/2024</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
@@ -4543,29 +4543,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Read Only</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Terminated</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>15/08/2024</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>27/08/2024</t>
-        </is>
-      </c>
+          <t>22/11/2024</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4580,17 +4576,17 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>SAP ERP</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Power User</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4600,7 +4596,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>06/07/2024</t>
+          <t>06/05/2024</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
@@ -4618,7 +4614,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4628,20 +4624,24 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Power User</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>21/01/2024</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr"/>
+          <t>05/03/2024</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>25/06/2024</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Read Only</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>28/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
@@ -4694,17 +4694,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Read Only</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>09/03/2024</t>
+          <t>13/10/2024</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
@@ -4732,17 +4732,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Concur</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>08/02/2024</t>
+          <t>15/12/2024</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
@@ -4775,7 +4775,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>SAP ERP</t>
+          <t>Concur</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>13/01/2024</t>
+          <t>10/10/2024</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
@@ -4808,17 +4808,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>Concur</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Read Only</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>08/06/2024</t>
+          <t>10/04/2024</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4856,20 +4856,24 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>02/03/2024</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
+          <t>15/08/2024</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>27/08/2024</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4889,12 +4893,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Concur</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4904,7 +4908,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20/08/2024</t>
+          <t>06/07/2024</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
@@ -4922,12 +4926,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>SAP ERP</t>
+          <t>Concur</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4942,7 +4946,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>27/04/2024</t>
+          <t>21/01/2024</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
@@ -4960,7 +4964,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4970,7 +4974,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Read Only</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4980,7 +4984,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>25/02/2024</t>
+          <t>28/12/2024</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
@@ -4998,12 +5002,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>SAP ERP</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -5018,7 +5022,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>14/04/2024</t>
+          <t>09/03/2024</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
@@ -5041,12 +5045,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>Concur</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Read Only</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5056,7 +5060,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>27/02/2024</t>
+          <t>08/02/2024</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
@@ -5074,17 +5078,17 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>SAP ERP</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Read Only</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5094,7 +5098,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>17/11/2024</t>
+          <t>13/01/2024</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
@@ -5117,12 +5121,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Read Only</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5132,7 +5136,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20/01/2024</t>
+          <t>08/06/2024</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
@@ -5150,12 +5154,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -5170,7 +5174,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>22/11/2024</t>
+          <t>02/03/2024</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
@@ -5188,17 +5192,17 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>SAP ERP</t>
+          <t>Concur</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5208,7 +5212,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>17/09/2024</t>
+          <t>20/08/2024</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
@@ -5226,17 +5230,17 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>SAP ERP</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Read Only</t>
+          <t>Power User</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5246,7 +5250,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>28/07/2024</t>
+          <t>27/04/2024</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
@@ -5264,17 +5268,17 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Power User</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5284,7 +5288,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>01/12/2024</t>
+          <t>25/02/2024</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
@@ -5302,17 +5306,17 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>SAP ERP</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Read Only</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5322,7 +5326,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>22/12/2024</t>
+          <t>14/04/2024</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
@@ -5345,12 +5349,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Read Only</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5360,7 +5364,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>12/01/2024</t>
+          <t>27/02/2024</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
@@ -5378,17 +5382,17 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Read Only</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5398,7 +5402,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>06/11/2024</t>
+          <t>17/11/2024</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
@@ -5416,17 +5420,17 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Read Only</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -5436,7 +5440,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>07/05/2024</t>
+          <t>20/01/2024</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
@@ -5454,17 +5458,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>SAP ERP</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Power User</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5474,7 +5478,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>17/05/2024</t>
+          <t>22/11/2024</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
@@ -5492,17 +5496,17 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>SAP ERP</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Power User</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5512,7 +5516,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>25/01/2024</t>
+          <t>17/09/2024</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
@@ -5530,12 +5534,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5550,7 +5554,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>11/11/2024</t>
+          <t>28/07/2024</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
@@ -5568,17 +5572,17 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Power User</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5588,7 +5592,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>15/12/2024</t>
+          <t>01/12/2024</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
@@ -5606,7 +5610,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -5626,7 +5630,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>23/08/2024</t>
+          <t>22/12/2024</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
@@ -5654,7 +5658,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Read Only</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5664,7 +5668,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>14/12/2024</t>
+          <t>12/01/2024</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
@@ -5682,17 +5686,17 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Concur</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5702,7 +5706,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>11/05/2024</t>
+          <t>06/11/2024</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -5720,17 +5724,17 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Power User</t>
+          <t>Read Only</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5740,7 +5744,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20/08/2024</t>
+          <t>07/05/2024</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
@@ -5763,7 +5767,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>SAP ERP</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5778,7 +5782,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>02/08/2024</t>
+          <t>17/05/2024</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
@@ -5796,17 +5800,17 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Power User</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5816,7 +5820,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>21/05/2024</t>
+          <t>25/01/2024</t>
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
@@ -5834,7 +5838,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -5844,24 +5848,20 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Read Only</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Terminated</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>22/12/2024</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>03/01/2024</t>
-        </is>
-      </c>
+          <t>11/11/2024</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5876,17 +5876,17 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Concur</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>26/11/2024</t>
+          <t>15/12/2024</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
@@ -5914,12 +5914,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>SAP ERP</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>12/11/2024</t>
+          <t>23/08/2024</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>SAP ERP</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Read Only</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>22/03/2024</t>
+          <t>14/12/2024</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
@@ -5990,17 +5990,17 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>Concur</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>11/05/2024</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>Veeva CRM</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>09/11/2024</t>
+          <t>20/08/2024</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
@@ -6066,17 +6066,17 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>SAP ERP</t>
+          <t>LIMS</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Power User</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>17/08/2024</t>
+          <t>02/08/2024</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
@@ -6104,17 +6104,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>SAP ERP</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Power User</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>23/05/2024</t>
+          <t>21/05/2024</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -6152,20 +6152,24 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>04/04/2024</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr"/>
+          <t>22/12/2024</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>03/01/2024</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6185,12 +6189,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LIMS</t>
+          <t>Concur</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -6200,7 +6204,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>15/12/2024</t>
+          <t>26/11/2024</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
@@ -6218,34 +6222,30 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>SAP ERP</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Read Only</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Terminated</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>18/09/2024</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>28/11/2024</t>
-        </is>
-      </c>
+          <t>12/11/2024</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6258,7 +6258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>USR10062</t>
+          <t>USR10070</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6357,12 +6357,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>USR10149</t>
+          <t>USR10083</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Read Only</t>
+          <t>Power User</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Veeva CRM</t>
+          <t>LIMS</t>
         </is>
       </c>
     </row>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>USR10033</t>
+          <t>USR10107</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Read Only</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>Concur</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>USR10105</t>
+          <t>USR10007</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Terminated</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -6432,397 +6432,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>USR10075</t>
+          <t>USR10047</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Power User</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Terminated</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>LIMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>USR10139</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Service Account</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Terminated</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Veeva CRM</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>USR10027</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Standard User</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Terminated</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>SAP ERP</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>USR10021</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Service Account</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Terminated</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>LIMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>USR10091</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Power User</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Terminated</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Concur</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>USR10083</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Terminated</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Concur</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>11</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>USR10071</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Service Account</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Active Directory</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>12</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>USR10143</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Veeva CRM</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>13</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>USR10007</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Concur</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>14</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>USR10056</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Service Account</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Veeva CRM</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>15</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>USR10080</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Service Account</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Concur</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>16</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>USR10081</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Concur</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>17</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>USR10140</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Service Account</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Concur</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>18</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>USR10068</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Service Account</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>LIMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>19</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>USR10111</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>SAP ERP</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>20</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>USR10139</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Service Account</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Terminated</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Veeva CRM</t>
         </is>
       </c>
     </row>
